--- a/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
+++ b/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\BCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7519D7CE-E98F-413E-A6DF-5C9601EE62D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278F3552-43BC-45DE-9C0A-8ADFD495AF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -55,6 +55,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -109,12 +112,6 @@
     <t>https://www.bls.gov/data/inflation_calculator.htm</t>
   </si>
   <si>
-    <t>2024 to 2012 USD</t>
-  </si>
-  <si>
-    <t>*inflation adjusted starting in 2025, so we use the 2024 currency year to adjust to 2012 $</t>
-  </si>
-  <si>
     <t>45Q tax credits include a commenced construction provision. Based on EIA data, we assume a construction timeline</t>
   </si>
   <si>
@@ -230,6 +227,12 @@
   </si>
   <si>
     <t>values for industry only to reflect the duration multiplier.</t>
+  </si>
+  <si>
+    <t>2025 to 2012 USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*26 U.S.C. 45Q(h): inflation adjustment applies to taxable years beginning after 2026, substituting 2025 for 1990 - so the $85 is in 2025 dollars and we use the 2025 currency year to adjust to 2012 $. Factor matches the model OCCF (0.713109). </t>
   </si>
 </sst>
 </file>
@@ -664,19 +667,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.81640625" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" customWidth="1"/>
-    <col min="4" max="4" width="30.54296875" customWidth="1"/>
+    <col min="1" max="1" width="41.85546875" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,33 +687,33 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>0.73</v>
+        <v>0.71310899999999999</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -718,13 +721,13 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -732,29 +735,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -767,12 +770,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1086F14D-0ABA-4CBC-A6C8-8AA6F7BA1ED0}">
   <dimension ref="A1:AE35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B1" s="6">
         <v>2021</v>
       </c>
@@ -864,9 +867,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -964,9 +967,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <f>IFERROR(IF(A3=1,1,INDEX($B$2:$AE$2,MATCH((B1-'BCS-DoSfCS'!$B$2),$B$1:$AE$1,0))),0)</f>
@@ -1089,22 +1092,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>2022</v>
       </c>
@@ -1115,19 +1118,19 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>24</v>
       </c>
       <c r="B12">
         <v>14</v>
@@ -1139,34 +1142,34 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>30</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1178,12 +1181,12 @@
         <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -1195,30 +1198,30 @@
         <v>53</v>
       </c>
       <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>38</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1230,9 +1233,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1244,59 +1247,59 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1310,13 +1313,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1411,7 +1414,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1423,55 +1426,55 @@
       </c>
       <c r="D2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="E2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="F2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="G2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="H2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="I2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="J2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="K2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="L2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="M2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="N2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="O2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="P2">
         <f>About!$B$11*About!$A$9</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1519,7 +1522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1531,99 +1534,99 @@
       </c>
       <c r="D3">
         <f>About!$B$11*About!$A$9*(1-Calculations!D3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="E3">
         <f>About!$B$11*About!$A$9*(1-Calculations!E3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="F3">
         <f>About!$B$11*About!$A$9*(1-Calculations!F3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="G3">
         <f>About!$B$11*About!$A$9*(1-Calculations!G3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="H3">
         <f>About!$B$11*About!$A$9*(1-Calculations!H3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="I3">
         <f>About!$B$11*About!$A$9*(1-Calculations!I3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="J3">
         <f>About!$B$11*About!$A$9*(1-Calculations!J3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="K3">
         <f>About!$B$11*About!$A$9*(1-Calculations!K3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="L3">
         <f>About!$B$11*About!$A$9*(1-Calculations!L3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="M3">
         <f>About!$B$11*About!$A$9*(1-Calculations!M3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="N3">
         <f>About!$B$11*About!$A$9*(1-Calculations!N3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="O3">
         <f>About!$B$11*About!$A$9*(1-Calculations!O3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="P3">
         <f>About!$B$11*About!$A$9*(1-Calculations!P3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="Q3">
         <f>About!$B$11*About!$A$9*(1-Calculations!Q3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="R3">
         <f>About!$B$11*About!$A$9*(1-Calculations!R3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="S3">
         <f>About!$B$11*About!$A$9*(1-Calculations!S3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="T3">
         <f>About!$B$11*About!$A$9*(1-Calculations!T3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="U3">
         <f>About!$B$11*About!$A$9*(1-Calculations!U3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="V3">
         <f>About!$B$11*About!$A$9*(1-Calculations!V3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="W3">
         <f>About!$B$11*About!$A$9*(1-Calculations!W3)</f>
-        <v>62.05</v>
+        <v>60.614264999999996</v>
       </c>
       <c r="X3">
         <f>About!$B$11*About!$A$9*(1-Calculations!X3)</f>
-        <v>49.64</v>
+        <v>48.491411999999997</v>
       </c>
       <c r="Y3">
         <f>About!$B$11*About!$A$9*(1-Calculations!Y3)</f>
-        <v>37.229999999999997</v>
+        <v>36.368558999999998</v>
       </c>
       <c r="Z3">
         <f>About!$B$11*About!$A$9*(1-Calculations!Z3)</f>
-        <v>24.819999999999993</v>
+        <v>24.245705999999991</v>
       </c>
       <c r="AA3">
         <f>About!$B$11*About!$A$9*(1-Calculations!AA3)</f>
-        <v>12.409999999999997</v>
+        <v>12.122852999999996</v>
       </c>
       <c r="AB3">
         <f>About!$B$11*About!$A$9*(1-Calculations!AB3)</f>
@@ -1653,9 +1656,9 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
